--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Smoked Salmon (Sliced)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>85.85</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>257.55</t>
-        </is>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>257.55</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Box Cake - 6x6x3</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.15</v>
       </c>
     </row>
     <row r="4">
@@ -504,20 +492,14 @@
           <t>Box Cake - 8x8x2.5</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4.73</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4.73</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.73</v>
       </c>
     </row>
     <row r="5">
@@ -531,20 +513,14 @@
           <t>Celsius - Vibe Peach, Tropical, Arctic</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>28.49</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>56.98</t>
-        </is>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="E5" t="n">
+        <v>56.98</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +530,14 @@
           <t>Container - Muffin (1 Pack)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11.05</v>
       </c>
     </row>
     <row r="7">
@@ -577,20 +547,14 @@
           <t>Hazelnut Coffee (Grounded, Bulk)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>38.00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>152.00</t>
-        </is>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>38</v>
+      </c>
+      <c r="E7" t="n">
+        <v>152</v>
       </c>
     </row>
     <row r="8">
@@ -604,20 +568,14 @@
           <t>Kilogram Chai Concentrate</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>86.10</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>86.10</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -631,20 +589,14 @@
           <t>Lid Espresso - 4oz</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="10">
@@ -658,20 +610,14 @@
           <t>Panini Sheets - 16x8 3/8</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>44.49</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>44.49</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>44.49</v>
+      </c>
+      <c r="E10" t="n">
+        <v>44.49</v>
       </c>
     </row>
     <row r="11">
@@ -685,20 +631,14 @@
           <t>Torani - Caramel Sauce</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -712,20 +652,14 @@
           <t>Torani - Dark Chocolate Sauce</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -739,20 +673,14 @@
           <t>Torani - Pumpkin Pie Sauce</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>18.25</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>18.25</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="E13" t="n">
+        <v>18.25</v>
       </c>
     </row>
     <row r="14">
@@ -762,20 +690,14 @@
           <t>Torani - White Chocolate Sauce</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -789,20 +711,14 @@
           <t>Wrap - Foil (9" x 10.75")</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -816,20 +732,14 @@
           <t>Wrap - Paper (15" x 10.75")</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>5.97</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>11.94</t>
-        </is>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11.94</v>
       </c>
     </row>
     <row r="17">
@@ -839,20 +749,14 @@
           <t>Employee Water</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>11.72</t>
-        </is>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11.72</v>
       </c>
     </row>
     <row r="18">
@@ -862,20 +766,14 @@
           <t>Red Bull</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="E18" t="n">
+        <v>42.85</v>
       </c>
     </row>
     <row r="19">
@@ -889,20 +787,14 @@
           <t>Grandma's Coffee Cake - Cinnamon</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="E19" t="n">
+        <v>18.35</v>
       </c>
     </row>
     <row r="20">
@@ -916,20 +808,14 @@
           <t>Grandma's Coffee Cake - Blueberry</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>36.70</t>
-        </is>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="E20" t="n">
+        <v>36.7</v>
       </c>
     </row>
     <row r="21">
@@ -943,20 +829,14 @@
           <t>Grandma's Coffee Cake - Apple</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="E21" t="n">
+        <v>18.35</v>
       </c>
     </row>
     <row r="22">
@@ -966,20 +846,14 @@
           <t>Java Box (96oz)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>83.29</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>83.29</t>
-        </is>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>83.29000000000001</v>
+      </c>
+      <c r="E22" t="n">
+        <v>83.29000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -989,20 +863,14 @@
           <t>Java Box (160oz)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>92.59</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>92.59</t>
-        </is>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="E23" t="n">
+        <v>92.59</v>
       </c>
     </row>
   </sheetData>

--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_20251114.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,6 +873,99 @@
         <v>92.59</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Flour - Millers Choice</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nuts - Walnut Halves &amp; Pieces</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PERF</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Vegan Egg</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="E26" t="n">
+        <v>99.59</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bag - Paper Windowed Bagel Chip (4.5x11.75)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>80.48999999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>80.48999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 12oz Bowl (Smoothie)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
